--- a/calendrier-blog.xlsx
+++ b/calendrier-blog.xlsx
@@ -15,8 +15,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +59,12 @@
       <color rgb="005c524a"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -79,8 +86,20 @@
         <fgColor rgb="00F5EFE0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5EFE0"/>
+        <bgColor rgb="00F5EFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C97B5A"/>
+        <bgColor rgb="00C97B5A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,11 +107,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C97B5A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C97B5A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C97B5A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C97B5A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,6 +147,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -459,13 +507,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -503,10 +551,8 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>22 avril 2026</t>
-        </is>
+      <c r="A2" s="9" t="n">
+        <v>46134</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -535,10 +581,8 @@
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>29 avril 2026</t>
-        </is>
+      <c r="A3" s="9" t="n">
+        <v>46141</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -567,10 +611,8 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>6 mai 2026</t>
-        </is>
+      <c r="A4" s="9" t="n">
+        <v>46148</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -599,10 +641,8 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>13 mai 2026</t>
-        </is>
+      <c r="A5" s="9" t="n">
+        <v>46155</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -627,6 +667,306 @@
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>blog-article-4.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Les signes qu'un chien est heureux</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Bien-être</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>4 min</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-5.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Comment reconnaître un animal stressé ?</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Conseils</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>L'importance de la routine chez le chien</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Conseils</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-7.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Pourquoi les animaux ont besoin d'attention humaine</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Bien-être</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>4 min</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Le rôle du jeu dans le bien-être animal</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Bien-être</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>4 min</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Pourquoi éviter les cages en garde ?</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Éthique</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-10.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Les besoins émotionnels des animaux</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Bien-être</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-11.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Chien ou chat : les différences en garde</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Conseils</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-12.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Comment améliorer le confort de son animal</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Pratique</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>4 min</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-13.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Les erreurs qui stressent les animaux</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Conseils</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Planifié</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>blog-article-14.html</t>
         </is>
       </c>
     </row>

--- a/calendrier-blog.xlsx
+++ b/calendrier-blog.xlsx
@@ -668,9 +668,9 @@
           <t>3 min</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Planifié</t>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Publié</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
